--- a/data/planillas/Maestra Canales.xlsx
+++ b/data/planillas/Maestra Canales.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2420,6 +2420,78 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y EXPORTADORA ESTADO LIMITADA</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>UnionX B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MineGroup SpA</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>UnionX B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Teknorpro Chile SpA</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>UnionX B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Shopify Lhotse, Ara Osswald</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Lhotse web</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Melollevo, Martin Novoa Oficial</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>UnionX web</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sanchez y Cia.</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>UnionX B2B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/planillas/Maestra Canales.xlsx
+++ b/data/planillas/Maestra Canales.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B172"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,247 +1643,247 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Empresas La Polar S.A.</t>
+          <t>Cliente Shopify</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Abc</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cliente Shopify</t>
+          <t>Mall Plaza Egaña</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mall Plaza Egaña</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mall Plaza Egaña</t>
+          <t>Mall Plaza Norte</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mall Plaza Egaña</t>
+          <t>Mall Plaza Norte</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mall Plaza Norte</t>
+          <t>Showtime SpA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mall Plaza Norte</t>
+          <t>CMR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Showtime SpA</t>
+          <t>Cliente Gran Venta Garage</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>Gran Venta Garage</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cliente Gran Venta Garage</t>
+          <t>LA VINOTECA SPA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gran Venta Garage</t>
+          <t>Vinoteca</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LA VINOTECA SPA</t>
+          <t>Dinasty Partners</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vinoteca</t>
+          <t>Corporativo</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dinasty Partners</t>
+          <t>Innovatek, Tamara Arredondo</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Innovatek, Tamara Arredondo</t>
+          <t>Bazar ED</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BazarED</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bazar ED</t>
+          <t>Jorgelis Flores</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BazarED</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jorgelis Flores</t>
+          <t>CENCOSUD RETAIL S.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Paris tienda</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CENCOSUD RETAIL S.A.</t>
+          <t>Sanchez y compañia limitada</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Paris tienda</t>
+          <t>Ferretería Higuerillas</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sanchez y compañia limitada</t>
+          <t>JOSE RIVERO LLAMAZALES Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ferretería Higuerillas</t>
+          <t>El Volcan</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JOSE RIVERO LLAMAZALES Y COMPANIA LIMITADA</t>
+          <t>SOHO MARKET</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>El Volcan</t>
+          <t>Soho Market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SOHO MARKET</t>
+          <t>Supermercado Valeria Giacobbe Dadal</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Soho Market</t>
+          <t>Super Valeria Zapallar</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Supermercado Valeria Giacobbe Dadal</t>
+          <t>Comercial Brisas SPA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Super Valeria Zapallar</t>
+          <t>Comercial Brisas</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Comercial Brisas SPA</t>
+          <t>abc S.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Comercial Brisas</t>
+          <t>Abc</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>abc S.A.</t>
+          <t>Falabella.com SPA, Cliente Falabella Fcom</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Abc</t>
+          <t>Falabella</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Falabella.com SPA, Cliente Falabella Fcom</t>
+          <t>Cliente Lokal cl</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Falabella</t>
+          <t>Lokal</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cliente Lokal cl</t>
+          <t>Mall Plaza Vespucio Sur</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lokal</t>
+          <t>Mall Plaza Vespucio</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Mall Plaza Vespucio Sur</t>
+          <t>mall vespucio</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1895,355 +1895,355 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>mall vespucio</t>
+          <t>Lokal SpA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mall Plaza Vespucio</t>
+          <t>Lokal</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lokal SpA</t>
+          <t>Casa Mila SpA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lokal</t>
+          <t>Casa Mila</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Casa Mila SpA</t>
+          <t>Comercializadora SP Digital SPA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Casa Mila</t>
+          <t>Sp Digital</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Comercializadora SP Digital SPA</t>
+          <t>Cliente Falabella Fcom</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sp Digital</t>
+          <t>Falabella</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cliente Falabella Fcom</t>
+          <t>Consumidor Final - Hites_Marketplace</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Falabella</t>
+          <t>Hites</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Consumidor Final - Hites_Marketplace</t>
+          <t>Celmedia Fidelizacion SPA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hites</t>
+          <t>Celmedia</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Celmedia Fidelizacion SPA</t>
+          <t>Consumidor Final - Apprecio - Chile - Marketplace</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Celmedia</t>
+          <t>Apprecio</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Consumidor Final - Apprecio - Chile - Marketplace</t>
+          <t>LOS BAGUALES DE LA HACIENDA SPA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apprecio</t>
+          <t>Los Baguales De La Hacienda Spa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LOS BAGUALES DE LA HACIENDA SPA</t>
+          <t>SUPERMERCADO PUCON ORIENTE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Los Baguales De La Hacienda Spa</t>
+          <t>Supermercado Pucón Oriente</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PUCON ORIENTE</t>
+          <t>DOBLE R RETAIL LIMITADA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supermercado Pucón Oriente</t>
+          <t>Doble R Retail Limitada</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DOBLE R RETAIL LIMITADA</t>
+          <t>AZUL MARINO SA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Doble R Retail Limitada</t>
+          <t>Azul Marino Sa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AZUL MARINO SA</t>
+          <t>Abasolo y Compañía ltda.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Azul Marino Sa</t>
+          <t>Abasolo Y Compañía Ltda.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Abasolo y Compañía ltda.</t>
+          <t>COMERCIAL AMAR URIBE Y CIA. LTDA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Abasolo Y Compañía Ltda.</t>
+          <t>Comercial Amar Uribe Y Cia. Ltda</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>COMERCIAL AMAR URIBE Y CIA. LTDA</t>
+          <t>COMERCIAL AMAR HERMANOS Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Comercial Amar Uribe Y Cia. Ltda</t>
+          <t>Comercial Amar Hermanos Y Compania Limitada</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>COMERCIAL AMAR HERMANOS Y COMPANIA LIMITADA</t>
+          <t>Frigorífico de Osorno S.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Comercial Amar Hermanos Y Compania Limitada</t>
+          <t>Frigorífico De Osorno S.A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Frigorífico de Osorno S.A.</t>
+          <t>Jaime Cid Becerra</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Frigorífico De Osorno S.A.</t>
+          <t>Jaime Cid Becerra</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jaime Cid Becerra</t>
+          <t>Inversiones tecnológicas sweet and gourmet Ltda.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jaime Cid Becerra</t>
+          <t>Inversiones Tecnológicas Sweet And Gourmet Ltda.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Inversiones tecnológicas sweet and gourmet Ltda.</t>
+          <t>Eliette Dufey</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Inversiones Tecnológicas Sweet And Gourmet Ltda.</t>
+          <t>Eliette Dufey</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Eliette Dufey</t>
+          <t>Distribuidora Furet</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Eliette Dufey</t>
+          <t>Distribuidora Furet</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Distribuidora Furet</t>
+          <t>Tecnoventas ltda</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Distribuidora Furet</t>
+          <t>Tecnoventas Ltda</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Tecnoventas ltda</t>
+          <t>MARIO EDUARDO BURZIO ONETO</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tecnoventas Ltda</t>
+          <t>Mario Eduardo Burzio Oneto</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MARIO EDUARDO BURZIO ONETO</t>
+          <t>Albasini e Hijos Limitada</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mario Eduardo Burzio Oneto</t>
+          <t>Albasini E Hijos Limitada</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Albasini e Hijos Limitada</t>
+          <t>Comercial Buffalos Sport Spa</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Albasini E Hijos Limitada</t>
+          <t>Comercial Buffalos Sport Spa</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Comercial Buffalos Sport Spa</t>
+          <t>Comercial ECCSA S A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Comercial Buffalos Sport Spa</t>
+          <t>Ripley tienda</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Comercial ECCSA S A</t>
+          <t>SPEEDREAMS SPA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ripley tienda</t>
+          <t>Speedreams</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Web - Prefijo LH (Lhotse Store)</t>
+          <t>Sanchez y Cia.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Lhotse web</t>
+          <t>Ferretería Higuerillas</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Web - Prefijo SH (Simplit Home)</t>
+          <t>Web - Prefijo LH (Lhotse Store)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Simplit web</t>
+          <t>Lhotse web</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Web - Prefijo # (Union X Web)</t>
+          <t>Web - Prefijo SH (Simplit Home)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UnionX web</t>
+          <t>Simplit web</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SALVAJE FILMS &amp; TRAVEL SPA</t>
+          <t>Web - Prefijo # (Union X Web)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>UnionX B2B</t>
+          <t>UnionX web</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sociedad de Publicidad Imagina Ltda</t>
+          <t>SALVAJE FILMS &amp; TRAVEL SPA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EQOFFICE SPA</t>
+          <t>Sociedad de Publicidad Imagina Ltda</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aquagro S.A.</t>
+          <t>EQOFFICE SPA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TECMAN INGENIERIA LIMITADA</t>
+          <t>Aquagro S.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2291,7 +2291,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AYMARA SPORTSWEAR SpA</t>
+          <t>TECMAN INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cooperativa Suenos de Pichihuedque</t>
+          <t>AYMARA SPORTSWEAR SpA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SPEEDREAMS SPA</t>
+          <t>Cooperativa Suenos de Pichihuedque</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2477,18 +2477,6 @@
       <c r="B171" t="inlineStr">
         <is>
           <t>UnionX web</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Sanchez y Cia.</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>UnionX B2B</t>
         </is>
       </c>
     </row>
